--- a/mode_docx_gen/part/lvttoc/ptoc2/PTOC2.xlsx
+++ b/mode_docx_gen/part/lvttoc/ptoc2/PTOC2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\24. МТЗ Т2\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvttoc\ptoc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D2BE6A-D764-4EE2-ACE6-E516E9D310D0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060"/>
+    <workbookView xWindow="11820" yWindow="9540" windowWidth="17700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="141">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -436,12 +437,21 @@
   <si>
     <t>0 - Деблокировка, 
 1 - Блокировка</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Iset</t>
+  </si>
+  <si>
+    <t>Icoarse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -458,7 +468,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +490,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,11 +532,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -827,25 +843,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="63.5703125" style="3" customWidth="1"/>
-    <col min="7" max="12" width="9.140625" style="3"/>
-    <col min="13" max="13" width="14.7109375" style="3" customWidth="1"/>
-    <col min="14" max="26" width="9.140625" style="3"/>
-    <col min="27" max="27" width="16.85546875" style="3" customWidth="1"/>
-    <col min="28" max="28" width="20.5703125" style="3" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="63.5703125" style="2" customWidth="1"/>
+    <col min="7" max="12" width="9.140625" style="2"/>
+    <col min="13" max="13" width="14.7109375" style="2" customWidth="1"/>
+    <col min="14" max="26" width="9.140625" style="2"/>
+    <col min="27" max="27" width="16.85546875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="20.5703125" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -936,1208 +952,1211 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4">
-        <v>1</v>
-      </c>
-      <c r="V2" s="4">
-        <v>0</v>
-      </c>
-      <c r="W2" s="4">
-        <v>1</v>
-      </c>
-      <c r="X2" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD2" s="4" t="s">
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD2" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>1</v>
-      </c>
-      <c r="V3" s="4">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4">
-        <v>1</v>
-      </c>
-      <c r="X3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD3" s="4" t="s">
+      <c r="N3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>1</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
+        <v>1</v>
+      </c>
+      <c r="X3" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="4" t="s">
+      <c r="T4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AB4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AC4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="s">
+      <c r="T5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AB5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AC5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD5" s="4" t="s">
+      <c r="AC5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>1</v>
-      </c>
-      <c r="V6" s="4">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4">
-        <v>1</v>
-      </c>
-      <c r="X6" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD6" s="4" t="s">
+      <c r="N6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD6" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="4" t="s">
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
-        <v>1</v>
-      </c>
-      <c r="V7" s="4">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4">
-        <v>1</v>
-      </c>
-      <c r="X7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD7" s="4" t="s">
+      <c r="N7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>1</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD7" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="4" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
-        <v>1</v>
-      </c>
-      <c r="V8" s="4">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4">
-        <v>1</v>
-      </c>
-      <c r="X8" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD8" s="4" t="s">
+      <c r="N8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="4" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>1</v>
-      </c>
-      <c r="V9" s="4">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4">
-        <v>1</v>
-      </c>
-      <c r="X9" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD9" s="4" t="s">
+      <c r="N9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>1</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1</v>
+      </c>
+      <c r="X9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD9" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="4" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>1</v>
-      </c>
-      <c r="V10" s="4">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4">
-        <v>1</v>
-      </c>
-      <c r="X10" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD10" s="4" t="s">
+      <c r="N10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD10" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="4">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4">
-        <v>1</v>
-      </c>
-      <c r="V11" s="4">
-        <v>0</v>
-      </c>
-      <c r="W11" s="4">
-        <v>1</v>
-      </c>
-      <c r="X11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD11" s="4" t="s">
+      <c r="N11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>1</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>1</v>
+      </c>
+      <c r="X11" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" s="4" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="P12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Q12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S12" s="4" t="s">
+      <c r="S12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T12" s="4">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4">
-        <v>1</v>
-      </c>
-      <c r="V12" s="4">
-        <v>0</v>
-      </c>
-      <c r="W12" s="4">
-        <v>1</v>
-      </c>
-      <c r="X12" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="4" t="s">
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AB12" s="4" t="s">
+      <c r="AB12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AC12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD12" s="4" t="s">
+      <c r="AC12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD12" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="4" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="4" t="s">
+      <c r="S13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4">
-        <v>1</v>
-      </c>
-      <c r="V13" s="4">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4">
-        <v>1</v>
-      </c>
-      <c r="X13" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="4" t="s">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>1</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1</v>
+      </c>
+      <c r="X13" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="AB13" s="4" t="s">
+      <c r="AB13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AC13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD13" s="4" t="s">
+      <c r="AC13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD13" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="4" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T14" s="4">
-        <v>0</v>
-      </c>
-      <c r="U14" s="4">
-        <v>1</v>
-      </c>
-      <c r="V14" s="4">
-        <v>0</v>
-      </c>
-      <c r="W14" s="4">
-        <v>1</v>
-      </c>
-      <c r="X14" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD14" s="4" t="s">
+      <c r="N14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>1</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1</v>
+      </c>
+      <c r="X14" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2225,11 +2244,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2304,7 +2323,7 @@
       <c r="Z16" s="2">
         <v>0</v>
       </c>
-      <c r="AA16" s="4" t="s">
+      <c r="AA16" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB16" s="2" t="s">
@@ -2316,18 +2335,21 @@
       <c r="AD16" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="AE16" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>124</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -2396,7 +2418,7 @@
       <c r="Z17" s="2">
         <v>0</v>
       </c>
-      <c r="AA17" s="4" t="s">
+      <c r="AA17" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB17" s="2" t="s">
@@ -2408,12 +2430,15 @@
       <c r="AD17" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="AE17" s="6" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2443,7 +2468,7 @@
       <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
@@ -2488,7 +2513,7 @@
       <c r="Z18" s="2">
         <v>0</v>
       </c>
-      <c r="AA18" s="4" t="s">
+      <c r="AA18" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB18" s="2" t="s">
@@ -2501,11 +2526,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2535,7 +2560,7 @@
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>1</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -2580,7 +2605,7 @@
       <c r="Z19" s="2">
         <v>0</v>
       </c>
-      <c r="AA19" s="4" t="s">
+      <c r="AA19" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB19" s="2" t="s">
@@ -2593,11 +2618,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2627,7 +2652,7 @@
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>1</v>
       </c>
       <c r="M20" s="2" t="s">
@@ -2672,18 +2697,18 @@
       <c r="Z20" s="2">
         <v>0</v>
       </c>
-      <c r="AA20" s="4" t="s">
+      <c r="AA20" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2765,11 +2790,11 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2851,11 +2876,11 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2937,11 +2962,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3016,7 +3041,7 @@
       <c r="Z24" s="2">
         <v>0</v>
       </c>
-      <c r="AA24" s="4" t="s">
+      <c r="AA24" s="3" t="s">
         <v>123</v>
       </c>
       <c r="AB24" s="2" t="s">
@@ -3028,9 +3053,12 @@
       <c r="AD24" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="AE24" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AD24">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3039,7 +3067,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
